--- a/stories/arbres/ATOM-REL.CON.003-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche. Maman dit : tu peux dire pardon. Gaston dit : pardon, Nina. Maman dit : tu peux proposer un geste. Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
+          <t>Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche.
+maman|Tu peux dire pardon.
+enfant-m|Pardon, Nina.
+maman|Tu peux proposer un geste.
+narrateur|Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste.
+maman|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le puzzle de Nina s'est défait. Que fait Gaston ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaston a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat du puzzle redevient entier. Papa reste assis près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Le puzzle de Nina s'est défait. Que fait Gaston ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Gaston a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Le chat du puzzle redevient entier. Papa reste assis près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaston dit pardon et propose un geste</t>
+          <t>Le chat du puzzle</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël défait le puzzle-chat de Nina. Il dit pardon. Il pose le museau. Nina a encore un peu de peine. Ils reconstruisent l'oreille, tout doux.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
+          <t>La couverture de laine gratte un peu. Elle est grise, pliée sur le canapé. L'horloge fait tic, puis tac. La boîte du puzzle est ouverte. Sur le couvercle, un chat orange. Une pièce montre une moustache. La moustache est blanche, toute fine. Un coussin rond a glissé au sol. Il est jaune, un peu aplati. La lampe fait un rond sur le tapis. Tu as vu le chat, Raphaël ? Oui, maman. Il a des moustaches. Je m'assois près de la lampe. La lampe est douce, pas trop forte. En ce moment, Nina pose le puzzle. Les pièces font déjà un chat. Le museau est presque fini. Raphaël s'approche pour voir. Le puzzle se défait. Les pièces glissent sur le tapis. Une oreille orange part sous la table. Nina a les yeux mouillés. Elle est triste. Le chat est défait. Nina a de la peine. Nina a de la peine, Raphaël. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Raphaël ramasse une pièce. Il pose le museau du chat. Je te remets le museau. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Raphaël. Tu attends un peu ? Oui, papa. L'horloge fait encore tic. La couverture gratte toujours. Nina tient une pièce contre sa joue. Tu as le temps, Nina. Le chat peut attendre une minute. Plus tard, Nina pose une oreille. L'oreille est orange, un peu ronde. Raphaël tend une pièce. Ils reconstruisent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Raphaël. C'est du bon travail. Nina a encore un peu de peine. C'est normal. Le chat redevient un chat, peu à peu. La moustache blanche attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche.
+          <t>narrateur|La couverture de laine gratte un peu.
+narrateur|Elle est grise, pliée sur le canapé.
+narrateur|L'horloge fait tic, puis tac.
+narrateur|La boîte du puzzle est ouverte.
+narrateur|Sur le couvercle, un chat orange.
+narrateur|Une pièce montre une moustache.
+narrateur|La moustache est blanche, toute fine.
+narrateur|Un coussin rond a glissé au sol.
+narrateur|Il est jaune, un peu aplati.
+narrateur|La lampe fait un rond sur le tapis.
+maman|Tu as vu le chat, Raphaël ?
+enfant-m|Oui, maman.
+enfant-m|Il a des moustaches.
+papa|Je m'assois près de la lampe.
+papa|La lampe est douce, pas trop forte.
+narrateur|En ce moment, Nina pose le puzzle.
+narrateur|Les pièces font déjà un chat.
+narrateur|Le museau est presque fini.
+narrateur|Raphaël s'approche pour voir.
+narrateur|Le puzzle se défait.
+narrateur|Les pièces glissent sur le tapis.
+narrateur|Une oreille orange part sous la table.
+narrateur|Nina a les yeux mouillés.
+narrateur|Elle est triste.
+narrateur|Le chat est défait.
+narrateur|Nina a de la peine.
+maman|Nina a de la peine, Raphaël.
 maman|Tu peux dire pardon.
 enfant-m|Pardon, Nina.
 maman|Tu peux proposer un geste.
-narrateur|Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste.
+narrateur|Raphaël ramasse une pièce.
+narrateur|Il pose le museau du chat.
+enfant-m|Je te remets le museau.
+narrateur|C'est un geste simple.
+narrateur|Nina regarde.
+narrateur|Elle reste un peu triste.
 maman|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.</t>
+maman|Le pardon n'efface pas tout de suite.
+narrateur|Papa s'assoit près de Nina.
+papa|On laisse du temps, Raphaël.
+papa|Tu attends un peu ?
+enfant-m|Oui, papa.
+narrateur|L'horloge fait encore tic.
+narrateur|La couverture gratte toujours.
+narrateur|Nina tient une pièce contre sa joue.
+papa|Tu as le temps, Nina.
+maman|Le chat peut attendre une minute.
+narrateur|Plus tard, Nina pose une oreille.
+narrateur|L'oreille est orange, un peu ronde.
+narrateur|Raphaël tend une pièce.
+narrateur|Ils reconstruisent doucement.
+narrateur|La peine reste un peu.
+maman|Tu as dit pardon.
+maman|Tu as proposé un geste.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+papa|Nina a encore un peu de peine.
+papa|C'est normal.
+narrateur|Le chat redevient un chat, peu à peu.
+narrateur|La moustache blanche attend encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>horloge,puzzle_pieces</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le puzzle de Nina s'est défait. Que fait Gaston ?</t>
+          <t>Le puzzle de Nina s'est défait. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le puzzle de Nina s'est défait. Que fait Gaston ?</t>
+          <t>narrateur|Le puzzle de Nina s'est défait.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaston a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>Raphaël a dit pardon. Il a proposé un geste. Il a posé le museau du chat. Bravo, Raphaël. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1744,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaston a dit pardon. Il a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>narrateur|Raphaël a dit pardon.
+narrateur|Il a proposé un geste.
+narrateur|Il a posé le museau du chat.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+papa|La peine de Nina reste un peu.
+enfant-m|J'ai dit pardon.
+maman|Oui.
+maman|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chat du puzzle redevient entier. Papa reste assis près d'eux.</t>
+          <t>Le chat du puzzle redevient entier. Nina pose encore une moustache. On reste près du tapis ? Oui, papa. La laine gratte, hein ? Un peu. La peine reste un peu. On laisse le temps. La lampe est encore douce. L'horloge fait tac, tout loin. Le coussin jaune est encore au sol. On le remettra plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1920,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chat du puzzle redevient entier. Papa reste assis près d'eux.</t>
+          <t>narrateur|Le chat du puzzle redevient entier.
+narrateur|Nina pose encore une moustache.
+papa|On reste près du tapis ?
+enfant-m|Oui, papa.
+maman|La laine gratte, hein ?
+enfant-m|Un peu.
+maman|La peine reste un peu.
+maman|On laisse le temps.
+papa|La lampe est encore douce.
+narrateur|L'horloge fait tac, tout loin.
+narrateur|Le coussin jaune est encore au sol.
+maman|On le remettra plus tard.
+enfant-m|D'accord, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai posé le museau. Bravo. Tu as fait du bon travail. Le chat orange a ses deux oreilles. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit pardon.
+enfant-m|J'ai posé le museau.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le chat orange a ses deux oreilles.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La couverture de laine gratte un peu. Elle est grise, pliée sur le canapé. L'horloge fait tic, puis tac. La boîte du puzzle est ouverte. Sur le couvercle, un chat orange. Une pièce montre une moustache. La moustache est blanche, toute fine. Un coussin rond a glissé au sol. Il est jaune, un peu aplati. La lampe fait un rond sur le tapis. Tu as vu le chat, Raphaël ? Oui, maman. Il a des moustaches. Je m'assois près de la lampe. La lampe est douce, pas trop forte. En ce moment, Nina pose le puzzle. Les pièces font déjà un chat. Le museau est presque fini. Raphaël s'approche pour voir. Le puzzle se défait. Les pièces glissent sur le tapis. Une oreille orange part sous la table. Nina a les yeux mouillés. Elle est triste. Le chat est défait. Nina a de la peine. Nina a de la peine, Raphaël. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Raphaël ramasse une pièce. Il pose le museau du chat. Je te remets le museau. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Raphaël. Tu attends un peu ? Oui, papa. L'horloge fait encore tic. La couverture gratte toujours. Nina tient une pièce contre sa joue. Tu as le temps, Nina. Le chat peut attendre une minute. Plus tard, Nina pose une oreille. L'oreille est orange, un peu ronde. Raphaël tend une pièce. Ils reconstruisent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Raphaël. C'est du bon travail. Nina a encore un peu de peine. C'est normal. Le chat redevient un chat, peu à peu. La moustache blanche attend encore.</t>
+          <t>La couverture de laine gratte un peu. Elle est grise, pliée sur le canapé. L'horloge fait tic, puis tac. La boîte du puzzle est ouverte. Sur le couvercle, un chat orange. Une pièce montre une moustache. La moustache est blanche, toute fine. Un coussin rond a glissé au sol. Il est jaune, un peu aplati. La lampe fait un rond sur le tapis. Tu as vu le chat, Raphaël ? Oui, maman. Il a des moustaches. Je m'assois près de la lampe. La lampe est douce, pas trop forte. En ce moment, Nina pose le puzzle. Les pièces font déjà un chat. Le museau est presque fini. Raphaël s'approche pour voir. Le puzzle se défait. Les pièces glissent sur le tapis. Une oreille orange part sous la table. Nina a les yeux mouillés. Elle est triste. Le chat est défait. Nina a de la peine. Nina a de la peine, Raphaël. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Raphaël ramasse une pièce. Il pose le museau du chat. Je te remets le museau. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Raphaël. Tu attends un peu ? Oui, papa. L'horloge fait encore tic. La couverture gratte toujours. Nina tient une pièce contre sa joue. Tu as le temps, Nina. Le chat peut attendre une minute. Plus tard, Nina pose une oreille. L'oreille est orange, un peu ronde. Raphaël tend une pièce. Ils reconstruisent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Raphaël. Nina a encore un peu de peine. C'est normal. Le chat redevient un chat, peu à peu. La moustache blanche attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaston joue dans le salon avec maman. Nina a posé un puzzle. Les pièces font un chat. Gaston passe trop près. Le puzzle se défait. Nina a les yeux mouillés. Elle est triste. Parce que le chat est défait, Nina a de la peine. Maman s'approche. Maman dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Gaston dit : pardon, Nina. Maman dit : tu peux proposer un geste. Gaston ramasse une pièce. Il pose le museau du chat. C'est un geste simple. Nina regarde. Elle reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. Gaston attend. Plus tard, Nina pose une oreille. Gaston tend une pièce. Ils reconstruisent doucement. La peine reste un peu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La couverture de laine gratte un peu. Elle est grise, pliée sur le canapé. L'horloge fait tic, puis tac. La boîte du puzzle est ouverte. Sur le couvercle, un chat orange. Une pièce montre une moustache. La moustache est blanche, toute fine. Un coussin rond a glissé au sol. Il est jaune, un peu aplati. La lampe fait un rond sur le tapis. Tu as vu le chat, Raphaël ? Oui, maman. Il a des moustaches. Je m'assois près de la lampe. La lampe est douce, pas trop forte. En ce moment, Nina pose le puzzle. Les pièces font déjà un chat. Le museau est presque fini. Raphaël s'approche pour voir. Le puzzle se défait. Les pièces glissent sur le tapis. Une oreille orange part sous la table. Nina a les yeux mouillés. Elle est triste. Le chat est défait. Nina a de la peine. Nina a de la peine, Raphaël. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Raphaël ramasse une pièce. Il pose le museau du chat. Je te remets le museau. C'est un geste simple. Nina regarde. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Papa s'assoit près de Nina. On laisse du temps, Raphaël. Tu attends un peu ? Oui, papa. L'horloge fait encore tic. La couverture gratte toujours. Nina tient une pièce contre sa joue. Tu as le temps, Nina. Le chat peut attendre une minute. Plus tard, Nina pose une oreille. L'oreille est orange, un peu ronde. Raphaël tend une pièce. Ils reconstruisent doucement. La peine reste un peu. Tu as dit pardon. Tu as proposé un geste. Bravo, Raphaël. Nina a encore un peu de peine. C'est normal. Le chat redevient un chat, peu à peu. La moustache blanche attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 maman|Tu as dit pardon.
 maman|Tu as proposé un geste.
 maman|Bravo, Raphaël.
-maman|C'est du bon travail.
 papa|Nina a encore un peu de peine.
 papa|C'est normal.
 narrateur|Le chat redevient un chat, peu à peu.
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le puzzle de Nina s'est défait. Que fait Gaston ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le puzzle de Nina s'est défait. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1574,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit pardon. Il a proposé un geste. Il a posé le museau du chat. Bravo, Raphaël. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Raphaël a dit pardon. Il a proposé un geste. Il a posé le museau du chat. Bravo, Raphaël. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaston a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Il a proposé un geste. La peine reste un peu. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a dit pardon. Il a proposé un geste. Il a posé le museau du chat. Bravo, Raphaël. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,14 +1746,12 @@
 narrateur|Il a proposé un geste.
 narrateur|Il a posé le museau du chat.
 maman|Bravo, Raphaël.
-maman|C'est du bon travail.
 papa|La peine de Nina reste un peu.
 enfant-m|J'ai dit pardon.
 maman|Oui.
 maman|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chat du puzzle redevient entier. Papa reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat du puzzle redevient entier. Nina pose encore une moustache. On reste près du tapis ? Oui, papa. La laine gratte, hein ? Un peu. La peine reste un peu. On laisse le temps. La lampe est encore douce. L'horloge fait tac, tout loin. Le coussin jaune est encore au sol. On le remettra plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 enfant-m|D'accord, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai posé le museau. Bravo. Tu as fait du bon travail. Le chat orange a ses deux oreilles. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai posé le museau. Bravo. Le chat orange a ses deux oreilles.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai posé le museau. Bravo. Le chat orange a ses deux oreilles.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-m|J'ai dit pardon.
 enfant-m|J'ai posé le museau.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le chat orange a ses deux oreilles.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le chat orange a ses deux oreilles.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-08.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaston, Nina, maman, papa</t>
+          <t>Raphaël, Nina, maman, papa</t>
         </is>
       </c>
     </row>
